--- a/1_network_estimation/1_data_cleaning/Data_clean/MCAS/Estados_US/Edos_USA_2021/WYOMING_2021.xlsx
+++ b/1_network_estimation/1_data_cleaning/Data_clean/MCAS/Estados_US/Edos_USA_2021/WYOMING_2021.xlsx
@@ -351,28 +351,28 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D286"/>
+  <dimension ref="A1:D280"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Estado de Origen</t>
+          <t>mx_state</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Municipio Origen</t>
+          <t>mx_municipality</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Número de Matrículas</t>
+          <t>n_matriculas</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Porcentaje de Matrículas</t>
+          <t>pct_matriculas</t>
         </is>
       </c>
     </row>
@@ -395,9 +395,14 @@
       </c>
     </row>
     <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Aguascalientes</t>
+        </is>
+      </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Pabellón de Arteaga</t>
+          <t>Pabellón De Arteaga</t>
         </is>
       </c>
       <c r="C3">
@@ -408,9 +413,14 @@
       </c>
     </row>
     <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Aguascalientes</t>
+        </is>
+      </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Rincón de Romos</t>
+          <t>Rincón De Romos</t>
         </is>
       </c>
       <c r="C4">
@@ -421,6 +431,11 @@
       </c>
     </row>
     <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Aguascalientes</t>
+        </is>
+      </c>
       <c r="B5" t="inlineStr">
         <is>
           <t>Tepezalá</t>
@@ -434,6 +449,11 @@
       </c>
     </row>
     <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Aguascalientes</t>
+        </is>
+      </c>
       <c r="B6" t="inlineStr">
         <is>
           <t>Total</t>
@@ -465,6 +485,11 @@
       </c>
     </row>
     <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Baja California</t>
+        </is>
+      </c>
       <c r="B8" t="inlineStr">
         <is>
           <t>Total</t>
@@ -496,6 +521,11 @@
       </c>
     </row>
     <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Campeche</t>
+        </is>
+      </c>
       <c r="B10" t="inlineStr">
         <is>
           <t>Total</t>
@@ -527,6 +557,11 @@
       </c>
     </row>
     <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B12" t="inlineStr">
         <is>
           <t>Total</t>
@@ -558,6 +593,11 @@
       </c>
     </row>
     <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B14" t="inlineStr">
         <is>
           <t>Allende</t>
@@ -571,6 +611,11 @@
       </c>
     </row>
     <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B15" t="inlineStr">
         <is>
           <t>Bachíniva</t>
@@ -584,6 +629,11 @@
       </c>
     </row>
     <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B16" t="inlineStr">
         <is>
           <t>Bocoyna</t>
@@ -597,6 +647,11 @@
       </c>
     </row>
     <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B17" t="inlineStr">
         <is>
           <t>Buenaventura</t>
@@ -610,6 +665,11 @@
       </c>
     </row>
     <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B18" t="inlineStr">
         <is>
           <t>Camargo</t>
@@ -623,6 +683,11 @@
       </c>
     </row>
     <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B19" t="inlineStr">
         <is>
           <t>Chihuahua</t>
@@ -636,6 +701,11 @@
       </c>
     </row>
     <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B20" t="inlineStr">
         <is>
           <t>Coronado</t>
@@ -649,6 +719,11 @@
       </c>
     </row>
     <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B21" t="inlineStr">
         <is>
           <t>Cuauhtémoc</t>
@@ -662,6 +737,11 @@
       </c>
     </row>
     <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B22" t="inlineStr">
         <is>
           <t>Delicias</t>
@@ -675,6 +755,11 @@
       </c>
     </row>
     <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B23" t="inlineStr">
         <is>
           <t>El Tule</t>
@@ -688,6 +773,11 @@
       </c>
     </row>
     <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B24" t="inlineStr">
         <is>
           <t>Guadalupe</t>
@@ -701,9 +791,14 @@
       </c>
     </row>
     <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Guadalupe y Calvo</t>
+          <t>Guadalupe Y Calvo</t>
         </is>
       </c>
       <c r="C25">
@@ -714,6 +809,11 @@
       </c>
     </row>
     <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B26" t="inlineStr">
         <is>
           <t>Guerrero</t>
@@ -727,9 +827,14 @@
       </c>
     </row>
     <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Hidalgo del Parral</t>
+          <t>Hidalgo Del Parral</t>
         </is>
       </c>
       <c r="C27">
@@ -740,6 +845,11 @@
       </c>
     </row>
     <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B28" t="inlineStr">
         <is>
           <t>Ignacio Zaragoza</t>
@@ -753,6 +863,11 @@
       </c>
     </row>
     <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B29" t="inlineStr">
         <is>
           <t>Juárez</t>
@@ -766,6 +881,11 @@
       </c>
     </row>
     <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B30" t="inlineStr">
         <is>
           <t>Madera</t>
@@ -779,6 +899,11 @@
       </c>
     </row>
     <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B31" t="inlineStr">
         <is>
           <t>Manuel Benavides</t>
@@ -792,6 +917,11 @@
       </c>
     </row>
     <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B32" t="inlineStr">
         <is>
           <t>Meoqui</t>
@@ -805,6 +935,11 @@
       </c>
     </row>
     <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B33" t="inlineStr">
         <is>
           <t>Morelos</t>
@@ -818,6 +953,11 @@
       </c>
     </row>
     <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B34" t="inlineStr">
         <is>
           <t>Namiquipa</t>
@@ -831,6 +971,11 @@
       </c>
     </row>
     <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B35" t="inlineStr">
         <is>
           <t>Nuevo Casas Grandes</t>
@@ -844,6 +989,11 @@
       </c>
     </row>
     <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B36" t="inlineStr">
         <is>
           <t>Rosario</t>
@@ -857,6 +1007,11 @@
       </c>
     </row>
     <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B37" t="inlineStr">
         <is>
           <t>Satevó</t>
@@ -870,6 +1025,11 @@
       </c>
     </row>
     <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B38" t="inlineStr">
         <is>
           <t>Saucillo</t>
@@ -883,6 +1043,11 @@
       </c>
     </row>
     <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B39" t="inlineStr">
         <is>
           <t>Total</t>
@@ -914,6 +1079,11 @@
       </c>
     </row>
     <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Coahuila</t>
+        </is>
+      </c>
       <c r="B41" t="inlineStr">
         <is>
           <t>Múzquiz</t>
@@ -927,6 +1097,11 @@
       </c>
     </row>
     <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Coahuila</t>
+        </is>
+      </c>
       <c r="B42" t="inlineStr">
         <is>
           <t>Saltillo</t>
@@ -940,6 +1115,11 @@
       </c>
     </row>
     <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Coahuila</t>
+        </is>
+      </c>
       <c r="B43" t="inlineStr">
         <is>
           <t>San Buenaventura</t>
@@ -953,6 +1133,11 @@
       </c>
     </row>
     <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Coahuila</t>
+        </is>
+      </c>
       <c r="B44" t="inlineStr">
         <is>
           <t>Torreón</t>
@@ -966,6 +1151,11 @@
       </c>
     </row>
     <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Coahuila</t>
+        </is>
+      </c>
       <c r="B45" t="inlineStr">
         <is>
           <t>Viesca</t>
@@ -979,6 +1169,11 @@
       </c>
     </row>
     <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Coahuila</t>
+        </is>
+      </c>
       <c r="B46" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1010,6 +1205,11 @@
       </c>
     </row>
     <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Colima</t>
+        </is>
+      </c>
       <c r="B48" t="inlineStr">
         <is>
           <t>Tecomán</t>
@@ -1023,6 +1223,11 @@
       </c>
     </row>
     <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Colima</t>
+        </is>
+      </c>
       <c r="B49" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1038,7 +1243,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Ciudad de México</t>
+          <t>Ciudad De México</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -1054,6 +1259,11 @@
       </c>
     </row>
     <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B51" t="inlineStr">
         <is>
           <t>Azcapotzalco</t>
@@ -1067,6 +1277,11 @@
       </c>
     </row>
     <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B52" t="inlineStr">
         <is>
           <t>Benito Juárez</t>
@@ -1080,6 +1295,11 @@
       </c>
     </row>
     <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B53" t="inlineStr">
         <is>
           <t>Cuauhtémoc</t>
@@ -1093,6 +1313,11 @@
       </c>
     </row>
     <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B54" t="inlineStr">
         <is>
           <t>Gustavo A. Madero</t>
@@ -1106,6 +1331,11 @@
       </c>
     </row>
     <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B55" t="inlineStr">
         <is>
           <t>Iztacalco</t>
@@ -1119,6 +1349,11 @@
       </c>
     </row>
     <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B56" t="inlineStr">
         <is>
           <t>Iztapalapa</t>
@@ -1132,6 +1367,11 @@
       </c>
     </row>
     <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B57" t="inlineStr">
         <is>
           <t>Miguel Hidalgo</t>
@@ -1145,6 +1385,11 @@
       </c>
     </row>
     <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B58" t="inlineStr">
         <is>
           <t>Milpa Alta</t>
@@ -1158,6 +1403,11 @@
       </c>
     </row>
     <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B59" t="inlineStr">
         <is>
           <t>Tláhuac</t>
@@ -1171,6 +1421,11 @@
       </c>
     </row>
     <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B60" t="inlineStr">
         <is>
           <t>Tlalpan</t>
@@ -1184,6 +1439,11 @@
       </c>
     </row>
     <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B61" t="inlineStr">
         <is>
           <t>Venustiano Carranza</t>
@@ -1197,6 +1457,11 @@
       </c>
     </row>
     <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B62" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1228,6 +1493,11 @@
       </c>
     </row>
     <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Durango</t>
+        </is>
+      </c>
       <c r="B64" t="inlineStr">
         <is>
           <t>El Oro</t>
@@ -1241,6 +1511,11 @@
       </c>
     </row>
     <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Durango</t>
+        </is>
+      </c>
       <c r="B65" t="inlineStr">
         <is>
           <t>General Simón Bolívar</t>
@@ -1254,6 +1529,11 @@
       </c>
     </row>
     <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Durango</t>
+        </is>
+      </c>
       <c r="B66" t="inlineStr">
         <is>
           <t>Lerdo</t>
@@ -1267,6 +1547,11 @@
       </c>
     </row>
     <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Durango</t>
+        </is>
+      </c>
       <c r="B67" t="inlineStr">
         <is>
           <t>Mezquital</t>
@@ -1280,6 +1565,11 @@
       </c>
     </row>
     <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Durango</t>
+        </is>
+      </c>
       <c r="B68" t="inlineStr">
         <is>
           <t>Ocampo</t>
@@ -1293,6 +1583,11 @@
       </c>
     </row>
     <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Durango</t>
+        </is>
+      </c>
       <c r="B69" t="inlineStr">
         <is>
           <t>San Bernardo</t>
@@ -1306,6 +1601,11 @@
       </c>
     </row>
     <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Durango</t>
+        </is>
+      </c>
       <c r="B70" t="inlineStr">
         <is>
           <t>Vicente Guerrero</t>
@@ -1319,6 +1619,11 @@
       </c>
     </row>
     <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Durango</t>
+        </is>
+      </c>
       <c r="B71" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1334,7 +1639,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Estado de México</t>
+          <t>Estado De México</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -1350,9 +1655,14 @@
       </c>
     </row>
     <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Atizapán de Zaragoza</t>
+          <t>Atizapán De Zaragoza</t>
         </is>
       </c>
       <c r="C73">
@@ -1363,6 +1673,11 @@
       </c>
     </row>
     <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B74" t="inlineStr">
         <is>
           <t>Chiautla</t>
@@ -1376,6 +1691,11 @@
       </c>
     </row>
     <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B75" t="inlineStr">
         <is>
           <t>Chicoloapan</t>
@@ -1389,6 +1709,11 @@
       </c>
     </row>
     <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B76" t="inlineStr">
         <is>
           <t>Chiconcuac</t>
@@ -1402,6 +1727,11 @@
       </c>
     </row>
     <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B77" t="inlineStr">
         <is>
           <t>Chimalhuacán</t>
@@ -1415,6 +1745,11 @@
       </c>
     </row>
     <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B78" t="inlineStr">
         <is>
           <t>Cuautitlán Izcalli</t>
@@ -1428,9 +1763,14 @@
       </c>
     </row>
     <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Ecatepec de Morelos</t>
+          <t>Ecatepec De Morelos</t>
         </is>
       </c>
       <c r="C79">
@@ -1441,9 +1781,14 @@
       </c>
     </row>
     <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Naucalpan de Juárez</t>
+          <t>Naucalpan De Juárez</t>
         </is>
       </c>
       <c r="C80">
@@ -1454,6 +1799,11 @@
       </c>
     </row>
     <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B81" t="inlineStr">
         <is>
           <t>Nezahualcóyotl</t>
@@ -1467,9 +1817,14 @@
       </c>
     </row>
     <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>San Felipe del Progreso</t>
+          <t>San Felipe Del Progreso</t>
         </is>
       </c>
       <c r="C82">
@@ -1480,9 +1835,14 @@
       </c>
     </row>
     <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>San Simón de Guerrero</t>
+          <t>San Simón De Guerrero</t>
         </is>
       </c>
       <c r="C83">
@@ -1493,6 +1853,11 @@
       </c>
     </row>
     <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B84" t="inlineStr">
         <is>
           <t>Tecámac</t>
@@ -1506,6 +1871,11 @@
       </c>
     </row>
     <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B85" t="inlineStr">
         <is>
           <t>Texcoco</t>
@@ -1519,9 +1889,14 @@
       </c>
     </row>
     <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Tlalnepantla de Baz</t>
+          <t>Tlalnepantla De Baz</t>
         </is>
       </c>
       <c r="C86">
@@ -1532,6 +1907,11 @@
       </c>
     </row>
     <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B87" t="inlineStr">
         <is>
           <t>Toluca</t>
@@ -1545,6 +1925,11 @@
       </c>
     </row>
     <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B88" t="inlineStr">
         <is>
           <t>Villa Victoria</t>
@@ -1558,6 +1943,11 @@
       </c>
     </row>
     <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B89" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1589,6 +1979,11 @@
       </c>
     </row>
     <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B91" t="inlineStr">
         <is>
           <t>Celaya</t>
@@ -1602,6 +1997,11 @@
       </c>
     </row>
     <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B92" t="inlineStr">
         <is>
           <t>Irapuato</t>
@@ -1615,6 +2015,11 @@
       </c>
     </row>
     <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B93" t="inlineStr">
         <is>
           <t>León</t>
@@ -1628,6 +2033,11 @@
       </c>
     </row>
     <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B94" t="inlineStr">
         <is>
           <t>Pénjamo</t>
@@ -1641,9 +2051,14 @@
       </c>
     </row>
     <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>San Francisco del Rincón</t>
+          <t>San Francisco Del Rincón</t>
         </is>
       </c>
       <c r="C95">
@@ -1654,6 +2069,11 @@
       </c>
     </row>
     <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B96" t="inlineStr">
         <is>
           <t>Uriangato</t>
@@ -1667,9 +2087,14 @@
       </c>
     </row>
     <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Valle de Santiago</t>
+          <t>Valle De Santiago</t>
         </is>
       </c>
       <c r="C97">
@@ -1680,6 +2105,11 @@
       </c>
     </row>
     <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B98" t="inlineStr">
         <is>
           <t>Yuriria</t>
@@ -1693,6 +2123,11 @@
       </c>
     </row>
     <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B99" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1713,7 +2148,7 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Acapulco de Juárez</t>
+          <t>Acapulco De Juárez</t>
         </is>
       </c>
       <c r="C100">
@@ -1724,6 +2159,11 @@
       </c>
     </row>
     <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B101" t="inlineStr">
         <is>
           <t>Arcelia</t>
@@ -1737,6 +2177,11 @@
       </c>
     </row>
     <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B102" t="inlineStr">
         <is>
           <t>Azoyú</t>
@@ -1750,9 +2195,14 @@
       </c>
     </row>
     <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Chilapa de Álvarez</t>
+          <t>Chilapa De Álvarez</t>
         </is>
       </c>
       <c r="C103">
@@ -1763,9 +2213,14 @@
       </c>
     </row>
     <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Chilpancingo de los Bravo</t>
+          <t>Chilpancingo De Los Bravo</t>
         </is>
       </c>
       <c r="C104">
@@ -1776,6 +2231,11 @@
       </c>
     </row>
     <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B105" t="inlineStr">
         <is>
           <t>Juan R. Escudero</t>
@@ -1789,6 +2249,11 @@
       </c>
     </row>
     <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B106" t="inlineStr">
         <is>
           <t>Ometepec</t>
@@ -1802,6 +2267,11 @@
       </c>
     </row>
     <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B107" t="inlineStr">
         <is>
           <t>Quechultenango</t>
@@ -1815,6 +2285,11 @@
       </c>
     </row>
     <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B108" t="inlineStr">
         <is>
           <t>Tlacoachistlahuaca</t>
@@ -1828,6 +2303,11 @@
       </c>
     </row>
     <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B109" t="inlineStr">
         <is>
           <t>Tlapehuala</t>
@@ -1841,6 +2321,11 @@
       </c>
     </row>
     <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B110" t="inlineStr">
         <is>
           <t>Xalpatláhuac</t>
@@ -1854,6 +2339,11 @@
       </c>
     </row>
     <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B111" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1885,6 +2375,11 @@
       </c>
     </row>
     <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B113" t="inlineStr">
         <is>
           <t>Metepec</t>
@@ -1898,6 +2393,11 @@
       </c>
     </row>
     <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B114" t="inlineStr">
         <is>
           <t>Pacula</t>
@@ -1911,9 +2411,14 @@
       </c>
     </row>
     <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Tulancingo de Bravo</t>
+          <t>Tulancingo De Bravo</t>
         </is>
       </c>
       <c r="C115">
@@ -1924,6 +2429,11 @@
       </c>
     </row>
     <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B116" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1955,6 +2465,11 @@
       </c>
     </row>
     <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B118" t="inlineStr">
         <is>
           <t>Arandas</t>
@@ -1968,6 +2483,11 @@
       </c>
     </row>
     <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B119" t="inlineStr">
         <is>
           <t>Ayotlán</t>
@@ -1981,6 +2501,11 @@
       </c>
     </row>
     <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B120" t="inlineStr">
         <is>
           <t>Ayutla</t>
@@ -1994,6 +2519,11 @@
       </c>
     </row>
     <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B121" t="inlineStr">
         <is>
           <t>Cabo Corrientes</t>
@@ -2007,6 +2537,11 @@
       </c>
     </row>
     <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B122" t="inlineStr">
         <is>
           <t>Chimaltitán</t>
@@ -2020,9 +2555,14 @@
       </c>
     </row>
     <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Cuautitlán de García Barragán</t>
+          <t>Cuautitlán De García Barragán</t>
         </is>
       </c>
       <c r="C123">
@@ -2033,9 +2573,14 @@
       </c>
     </row>
     <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Encarnación de Díaz</t>
+          <t>Encarnación De Díaz</t>
         </is>
       </c>
       <c r="C124">
@@ -2046,6 +2591,11 @@
       </c>
     </row>
     <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B125" t="inlineStr">
         <is>
           <t>Etzatlán</t>
@@ -2059,6 +2609,11 @@
       </c>
     </row>
     <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B126" t="inlineStr">
         <is>
           <t>Guadalajara</t>
@@ -2072,6 +2627,11 @@
       </c>
     </row>
     <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B127" t="inlineStr">
         <is>
           <t>La Huerta</t>
@@ -2085,9 +2645,14 @@
       </c>
     </row>
     <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Lagos de Moreno</t>
+          <t>Lagos De Moreno</t>
         </is>
       </c>
       <c r="C128">
@@ -2098,6 +2663,11 @@
       </c>
     </row>
     <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B129" t="inlineStr">
         <is>
           <t>Magdalena</t>
@@ -2111,6 +2681,11 @@
       </c>
     </row>
     <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B130" t="inlineStr">
         <is>
           <t>Ocotlán</t>
@@ -2124,6 +2699,11 @@
       </c>
     </row>
     <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B131" t="inlineStr">
         <is>
           <t>Pihuamo</t>
@@ -2137,9 +2717,14 @@
       </c>
     </row>
     <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>San Cristóbal de la Barranca</t>
+          <t>San Cristóbal De La Barranca</t>
         </is>
       </c>
       <c r="C132">
@@ -2150,9 +2735,14 @@
       </c>
     </row>
     <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>San Diego de Alejandría</t>
+          <t>San Diego De Alejandría</t>
         </is>
       </c>
       <c r="C133">
@@ -2163,9 +2753,14 @@
       </c>
     </row>
     <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>San Juan de los Lagos</t>
+          <t>San Juan De Los Lagos</t>
         </is>
       </c>
       <c r="C134">
@@ -2176,6 +2771,11 @@
       </c>
     </row>
     <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B135" t="inlineStr">
         <is>
           <t>Tala</t>
@@ -2189,6 +2789,11 @@
       </c>
     </row>
     <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B136" t="inlineStr">
         <is>
           <t>Teocaltiche</t>
@@ -2202,9 +2807,14 @@
       </c>
     </row>
     <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Tizapán el Alto</t>
+          <t>Tizapán El Alto</t>
         </is>
       </c>
       <c r="C137">
@@ -2215,9 +2825,14 @@
       </c>
     </row>
     <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Tlajomulco de Zúñiga</t>
+          <t>Tlajomulco De Zúñiga</t>
         </is>
       </c>
       <c r="C138">
@@ -2228,6 +2843,11 @@
       </c>
     </row>
     <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B139" t="inlineStr">
         <is>
           <t>San Pedro Tlaquepaque</t>
@@ -2241,9 +2861,14 @@
       </c>
     </row>
     <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Unión de Tula</t>
+          <t>Unión De Tula</t>
         </is>
       </c>
       <c r="C140">
@@ -2254,6 +2879,11 @@
       </c>
     </row>
     <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B141" t="inlineStr">
         <is>
           <t>Villa Corona</t>
@@ -2267,6 +2897,11 @@
       </c>
     </row>
     <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B142" t="inlineStr">
         <is>
           <t>Villa Hidalgo</t>
@@ -2280,6 +2915,11 @@
       </c>
     </row>
     <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B143" t="inlineStr">
         <is>
           <t>Villa Purificación</t>
@@ -2293,6 +2933,11 @@
       </c>
     </row>
     <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B144" t="inlineStr">
         <is>
           <t>Zapopan</t>
@@ -2306,9 +2951,14 @@
       </c>
     </row>
     <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Zapotlán el Grande</t>
+          <t>Zapotlán El Grande</t>
         </is>
       </c>
       <c r="C145">
@@ -2319,6 +2969,11 @@
       </c>
     </row>
     <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B146" t="inlineStr">
         <is>
           <t>Total</t>
@@ -2350,6 +3005,11 @@
       </c>
     </row>
     <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B148" t="inlineStr">
         <is>
           <t>Álvaro Obregón</t>
@@ -2363,6 +3023,11 @@
       </c>
     </row>
     <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B149" t="inlineStr">
         <is>
           <t>Apatzingán</t>
@@ -2376,6 +3041,11 @@
       </c>
     </row>
     <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B150" t="inlineStr">
         <is>
           <t>Carácuaro</t>
@@ -2389,6 +3059,11 @@
       </c>
     </row>
     <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B151" t="inlineStr">
         <is>
           <t>Irimbo</t>
@@ -2402,6 +3077,11 @@
       </c>
     </row>
     <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B152" t="inlineStr">
         <is>
           <t>Ixtlán</t>
@@ -2415,6 +3095,11 @@
       </c>
     </row>
     <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B153" t="inlineStr">
         <is>
           <t>Jiménez</t>
@@ -2428,6 +3113,11 @@
       </c>
     </row>
     <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B154" t="inlineStr">
         <is>
           <t>La Piedad</t>
@@ -2441,6 +3131,11 @@
       </c>
     </row>
     <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B155" t="inlineStr">
         <is>
           <t>Morelia</t>
@@ -2454,6 +3149,11 @@
       </c>
     </row>
     <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B156" t="inlineStr">
         <is>
           <t>Nocupétaro</t>
@@ -2467,6 +3167,11 @@
       </c>
     </row>
     <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B157" t="inlineStr">
         <is>
           <t>Parácuaro</t>
@@ -2480,6 +3185,11 @@
       </c>
     </row>
     <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B158" t="inlineStr">
         <is>
           <t>Peribán</t>
@@ -2493,6 +3203,11 @@
       </c>
     </row>
     <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B159" t="inlineStr">
         <is>
           <t>Queréndaro</t>
@@ -2506,6 +3221,11 @@
       </c>
     </row>
     <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B160" t="inlineStr">
         <is>
           <t>Tangancícuaro</t>
@@ -2519,6 +3239,11 @@
       </c>
     </row>
     <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B161" t="inlineStr">
         <is>
           <t>Tepalcatepec</t>
@@ -2532,6 +3257,11 @@
       </c>
     </row>
     <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B162" t="inlineStr">
         <is>
           <t>Turicato</t>
@@ -2545,6 +3275,11 @@
       </c>
     </row>
     <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B163" t="inlineStr">
         <is>
           <t>Tuxpan</t>
@@ -2558,6 +3293,11 @@
       </c>
     </row>
     <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B164" t="inlineStr">
         <is>
           <t>Uruapan</t>
@@ -2571,6 +3311,11 @@
       </c>
     </row>
     <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B165" t="inlineStr">
         <is>
           <t>Zacapu</t>
@@ -2584,6 +3329,11 @@
       </c>
     </row>
     <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B166" t="inlineStr">
         <is>
           <t>Zamora</t>
@@ -2597,6 +3347,11 @@
       </c>
     </row>
     <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B167" t="inlineStr">
         <is>
           <t>Total</t>
@@ -2628,6 +3383,11 @@
       </c>
     </row>
     <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>Morelos</t>
+        </is>
+      </c>
       <c r="B169" t="inlineStr">
         <is>
           <t>Miacatlán</t>
@@ -2641,9 +3401,14 @@
       </c>
     </row>
     <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>Morelos</t>
+        </is>
+      </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Tetela del Volcán</t>
+          <t>Tetela Del Volcán</t>
         </is>
       </c>
       <c r="C170">
@@ -2654,6 +3419,11 @@
       </c>
     </row>
     <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>Morelos</t>
+        </is>
+      </c>
       <c r="B171" t="inlineStr">
         <is>
           <t>Total</t>
@@ -2674,7 +3444,7 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Amatlán de Cañas</t>
+          <t>Amatlán De Cañas</t>
         </is>
       </c>
       <c r="C172">
@@ -2685,6 +3455,11 @@
       </c>
     </row>
     <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>Nayarit</t>
+        </is>
+      </c>
       <c r="B173" t="inlineStr">
         <is>
           <t>Huajicori</t>
@@ -2698,9 +3473,14 @@
       </c>
     </row>
     <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>Nayarit</t>
+        </is>
+      </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Ixtlán del Río</t>
+          <t>Ixtlán Del Río</t>
         </is>
       </c>
       <c r="C174">
@@ -2711,6 +3491,11 @@
       </c>
     </row>
     <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>Nayarit</t>
+        </is>
+      </c>
       <c r="B175" t="inlineStr">
         <is>
           <t>Ruíz</t>
@@ -2724,9 +3509,14 @@
       </c>
     </row>
     <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>Nayarit</t>
+        </is>
+      </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Santa María del Oro</t>
+          <t>Santa María Del Oro</t>
         </is>
       </c>
       <c r="C176">
@@ -2737,6 +3527,11 @@
       </c>
     </row>
     <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>Nayarit</t>
+        </is>
+      </c>
       <c r="B177" t="inlineStr">
         <is>
           <t>Tepic</t>
@@ -2750,6 +3545,11 @@
       </c>
     </row>
     <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>Nayarit</t>
+        </is>
+      </c>
       <c r="B178" t="inlineStr">
         <is>
           <t>Total</t>
@@ -2781,6 +3581,11 @@
       </c>
     </row>
     <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>Nuevo León</t>
+        </is>
+      </c>
       <c r="B180" t="inlineStr">
         <is>
           <t>Total</t>
@@ -2801,7 +3606,7 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Coicoyán de las Flores</t>
+          <t>Coicoyán De Las Flores</t>
         </is>
       </c>
       <c r="C181">
@@ -2812,9 +3617,14 @@
       </c>
     </row>
     <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Oaxaca de Juárez</t>
+          <t>Oaxaca De Juárez</t>
         </is>
       </c>
       <c r="C182">
@@ -2825,9 +3635,14 @@
       </c>
     </row>
     <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Putla Villa de Guerrero</t>
+          <t>Putla Villa De Guerrero</t>
         </is>
       </c>
       <c r="C183">
@@ -2838,6 +3653,11 @@
       </c>
     </row>
     <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B184" t="inlineStr">
         <is>
           <t>San Juan Bautista Tuxtepec</t>
@@ -2851,6 +3671,11 @@
       </c>
     </row>
     <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B185" t="inlineStr">
         <is>
           <t>Santiago Amoltepec</t>
@@ -2864,6 +3689,11 @@
       </c>
     </row>
     <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B186" t="inlineStr">
         <is>
           <t>Santiago Yosondúa</t>
@@ -2877,6 +3707,11 @@
       </c>
     </row>
     <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B187" t="inlineStr">
         <is>
           <t>Santo Domingo Tepuxtepec</t>
@@ -2890,6 +3725,11 @@
       </c>
     </row>
     <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B188" t="inlineStr">
         <is>
           <t>Total</t>
@@ -2921,6 +3761,11 @@
       </c>
     </row>
     <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B190" t="inlineStr">
         <is>
           <t>Chignahuapan</t>
@@ -2934,6 +3779,11 @@
       </c>
     </row>
     <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B191" t="inlineStr">
         <is>
           <t>Esperanza</t>
@@ -2947,6 +3797,11 @@
       </c>
     </row>
     <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B192" t="inlineStr">
         <is>
           <t>Ixtacamaxtitlán</t>
@@ -2960,9 +3815,14 @@
       </c>
     </row>
     <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>Los Reyes de Juárez</t>
+          <t>Los Reyes De Juárez</t>
         </is>
       </c>
       <c r="C193">
@@ -2973,6 +3833,11 @@
       </c>
     </row>
     <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B194" t="inlineStr">
         <is>
           <t>Puebla</t>
@@ -2986,6 +3851,11 @@
       </c>
     </row>
     <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B195" t="inlineStr">
         <is>
           <t>San Miguel Xoxtla</t>
@@ -2999,9 +3869,14 @@
       </c>
     </row>
     <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>Tlacotepec de Benito Juárez</t>
+          <t>Tlacotepec De Benito Juárez</t>
         </is>
       </c>
       <c r="C196">
@@ -3012,6 +3887,11 @@
       </c>
     </row>
     <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B197" t="inlineStr">
         <is>
           <t>Tlapacoya</t>
@@ -3025,6 +3905,11 @@
       </c>
     </row>
     <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B198" t="inlineStr">
         <is>
           <t>Vicente Guerrero</t>
@@ -3038,6 +3923,11 @@
       </c>
     </row>
     <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B199" t="inlineStr">
         <is>
           <t>Yehualtepec</t>
@@ -3051,6 +3941,11 @@
       </c>
     </row>
     <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B200" t="inlineStr">
         <is>
           <t>Total</t>
@@ -3071,7 +3966,7 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>Amealco de Bonfil</t>
+          <t>Amealco De Bonfil</t>
         </is>
       </c>
       <c r="C201">
@@ -3082,9 +3977,14 @@
       </c>
     </row>
     <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>Querétaro</t>
+        </is>
+      </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>San Juan del Río</t>
+          <t>San Juan Del Río</t>
         </is>
       </c>
       <c r="C202">
@@ -3095,6 +3995,11 @@
       </c>
     </row>
     <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>Querétaro</t>
+        </is>
+      </c>
       <c r="B203" t="inlineStr">
         <is>
           <t>Tolimán</t>
@@ -3108,6 +4013,11 @@
       </c>
     </row>
     <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>Querétaro</t>
+        </is>
+      </c>
       <c r="B204" t="inlineStr">
         <is>
           <t>Total</t>
@@ -3139,6 +4049,11 @@
       </c>
     </row>
     <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B206" t="inlineStr">
         <is>
           <t>Rioverde</t>
@@ -3152,6 +4067,11 @@
       </c>
     </row>
     <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B207" t="inlineStr">
         <is>
           <t>Salinas</t>
@@ -3165,6 +4085,11 @@
       </c>
     </row>
     <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B208" t="inlineStr">
         <is>
           <t>San Luis Potosí</t>
@@ -3178,6 +4103,11 @@
       </c>
     </row>
     <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B209" t="inlineStr">
         <is>
           <t>Tierra Nueva</t>
@@ -3191,6 +4121,11 @@
       </c>
     </row>
     <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B210" t="inlineStr">
         <is>
           <t>Total</t>
@@ -3222,6 +4157,11 @@
       </c>
     </row>
     <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>Sinaloa</t>
+        </is>
+      </c>
       <c r="B212" t="inlineStr">
         <is>
           <t>Badiraguato</t>
@@ -3235,6 +4175,11 @@
       </c>
     </row>
     <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>Sinaloa</t>
+        </is>
+      </c>
       <c r="B213" t="inlineStr">
         <is>
           <t>Culiacán</t>
@@ -3248,6 +4193,11 @@
       </c>
     </row>
     <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>Sinaloa</t>
+        </is>
+      </c>
       <c r="B214" t="inlineStr">
         <is>
           <t>Guasave</t>
@@ -3261,6 +4211,11 @@
       </c>
     </row>
     <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>Sinaloa</t>
+        </is>
+      </c>
       <c r="B215" t="inlineStr">
         <is>
           <t>Total</t>
@@ -3292,6 +4247,11 @@
       </c>
     </row>
     <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>Sonora</t>
+        </is>
+      </c>
       <c r="B217" t="inlineStr">
         <is>
           <t>Bacerac</t>
@@ -3305,6 +4265,11 @@
       </c>
     </row>
     <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>Sonora</t>
+        </is>
+      </c>
       <c r="B218" t="inlineStr">
         <is>
           <t>Cajeme</t>
@@ -3318,6 +4283,11 @@
       </c>
     </row>
     <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>Sonora</t>
+        </is>
+      </c>
       <c r="B219" t="inlineStr">
         <is>
           <t>Empalme</t>
@@ -3331,6 +4301,11 @@
       </c>
     </row>
     <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>Sonora</t>
+        </is>
+      </c>
       <c r="B220" t="inlineStr">
         <is>
           <t>Guaymas</t>
@@ -3344,6 +4319,11 @@
       </c>
     </row>
     <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>Sonora</t>
+        </is>
+      </c>
       <c r="B221" t="inlineStr">
         <is>
           <t>Hermosillo</t>
@@ -3357,9 +4337,14 @@
       </c>
     </row>
     <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>Sonora</t>
+        </is>
+      </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>Nacozari de García</t>
+          <t>Nacozari De García</t>
         </is>
       </c>
       <c r="C222">
@@ -3370,6 +4355,11 @@
       </c>
     </row>
     <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>Sonora</t>
+        </is>
+      </c>
       <c r="B223" t="inlineStr">
         <is>
           <t>Nogales</t>
@@ -3383,6 +4373,11 @@
       </c>
     </row>
     <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>Sonora</t>
+        </is>
+      </c>
       <c r="B224" t="inlineStr">
         <is>
           <t>Sahuaripa</t>
@@ -3396,6 +4391,11 @@
       </c>
     </row>
     <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>Sonora</t>
+        </is>
+      </c>
       <c r="B225" t="inlineStr">
         <is>
           <t>San Luis Río Colorado</t>
@@ -3409,6 +4409,11 @@
       </c>
     </row>
     <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>Sonora</t>
+        </is>
+      </c>
       <c r="B226" t="inlineStr">
         <is>
           <t>Total</t>
@@ -3440,6 +4445,11 @@
       </c>
     </row>
     <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>Tabasco</t>
+        </is>
+      </c>
       <c r="B228" t="inlineStr">
         <is>
           <t>Centro</t>
@@ -3453,6 +4463,11 @@
       </c>
     </row>
     <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>Tabasco</t>
+        </is>
+      </c>
       <c r="B229" t="inlineStr">
         <is>
           <t>Huimanguillo</t>
@@ -3466,6 +4481,11 @@
       </c>
     </row>
     <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>Tabasco</t>
+        </is>
+      </c>
       <c r="B230" t="inlineStr">
         <is>
           <t>Total</t>
@@ -3497,6 +4517,11 @@
       </c>
     </row>
     <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>Tamaulipas</t>
+        </is>
+      </c>
       <c r="B232" t="inlineStr">
         <is>
           <t>Total</t>
@@ -3528,6 +4553,11 @@
       </c>
     </row>
     <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>Tlaxcala</t>
+        </is>
+      </c>
       <c r="B234" t="inlineStr">
         <is>
           <t>Atlangatepec</t>
@@ -3541,6 +4571,11 @@
       </c>
     </row>
     <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>Tlaxcala</t>
+        </is>
+      </c>
       <c r="B235" t="inlineStr">
         <is>
           <t>Calpulalpan</t>
@@ -3554,6 +4589,11 @@
       </c>
     </row>
     <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>Tlaxcala</t>
+        </is>
+      </c>
       <c r="B236" t="inlineStr">
         <is>
           <t>Chiautempan</t>
@@ -3567,6 +4607,11 @@
       </c>
     </row>
     <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>Tlaxcala</t>
+        </is>
+      </c>
       <c r="B237" t="inlineStr">
         <is>
           <t>Cuaxomulco</t>
@@ -3580,6 +4625,11 @@
       </c>
     </row>
     <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>Tlaxcala</t>
+        </is>
+      </c>
       <c r="B238" t="inlineStr">
         <is>
           <t>Hueyotlipan</t>
@@ -3593,9 +4643,14 @@
       </c>
     </row>
     <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>Tlaxcala</t>
+        </is>
+      </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>Muñoz de Domingo Arenas</t>
+          <t>Muñoz De Domingo Arenas</t>
         </is>
       </c>
       <c r="C239">
@@ -3606,6 +4661,11 @@
       </c>
     </row>
     <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>Tlaxcala</t>
+        </is>
+      </c>
       <c r="B240" t="inlineStr">
         <is>
           <t>Panotla</t>
@@ -3619,9 +4679,14 @@
       </c>
     </row>
     <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>Tlaxcala</t>
+        </is>
+      </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>Tepetitla de Lardizábal</t>
+          <t>Tepetitla De Lardizábal</t>
         </is>
       </c>
       <c r="C241">
@@ -3632,6 +4697,11 @@
       </c>
     </row>
     <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>Tlaxcala</t>
+        </is>
+      </c>
       <c r="B242" t="inlineStr">
         <is>
           <t>Terrenate</t>
@@ -3645,6 +4715,11 @@
       </c>
     </row>
     <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>Tlaxcala</t>
+        </is>
+      </c>
       <c r="B243" t="inlineStr">
         <is>
           <t>Tlaxcala</t>
@@ -3658,6 +4733,11 @@
       </c>
     </row>
     <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>Tlaxcala</t>
+        </is>
+      </c>
       <c r="B244" t="inlineStr">
         <is>
           <t>Tlaxco</t>
@@ -3671,6 +4751,11 @@
       </c>
     </row>
     <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>Tlaxcala</t>
+        </is>
+      </c>
       <c r="B245" t="inlineStr">
         <is>
           <t>Xaltocan</t>
@@ -3684,6 +4769,11 @@
       </c>
     </row>
     <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>Tlaxcala</t>
+        </is>
+      </c>
       <c r="B246" t="inlineStr">
         <is>
           <t>Yauhquemehcan</t>
@@ -3697,6 +4787,11 @@
       </c>
     </row>
     <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>Tlaxcala</t>
+        </is>
+      </c>
       <c r="B247" t="inlineStr">
         <is>
           <t>Zacatelco</t>
@@ -3710,6 +4805,11 @@
       </c>
     </row>
     <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>Tlaxcala</t>
+        </is>
+      </c>
       <c r="B248" t="inlineStr">
         <is>
           <t>Total</t>
@@ -3741,9 +4841,14 @@
       </c>
     </row>
     <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>Cosamaloapan de Carpio</t>
+          <t>Cosamaloapan De Carpio</t>
         </is>
       </c>
       <c r="C250">
@@ -3754,9 +4859,14 @@
       </c>
     </row>
     <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>Martínez de la Torre</t>
+          <t>Martínez De La Torre</t>
         </is>
       </c>
       <c r="C251">
@@ -3767,6 +4877,11 @@
       </c>
     </row>
     <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B252" t="inlineStr">
         <is>
           <t>Omealca</t>
@@ -3780,6 +4895,11 @@
       </c>
     </row>
     <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B253" t="inlineStr">
         <is>
           <t>Orizaba</t>
@@ -3793,6 +4913,11 @@
       </c>
     </row>
     <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B254" t="inlineStr">
         <is>
           <t>Pánuco</t>
@@ -3806,6 +4931,11 @@
       </c>
     </row>
     <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B255" t="inlineStr">
         <is>
           <t>Soteapan</t>
@@ -3819,6 +4949,11 @@
       </c>
     </row>
     <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B256" t="inlineStr">
         <is>
           <t>Tempoal</t>
@@ -3832,6 +4967,11 @@
       </c>
     </row>
     <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B257" t="inlineStr">
         <is>
           <t>Xalapa</t>
@@ -3845,6 +4985,11 @@
       </c>
     </row>
     <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B258" t="inlineStr">
         <is>
           <t>Total</t>
@@ -3876,6 +5021,11 @@
       </c>
     </row>
     <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>Yucatán</t>
+        </is>
+      </c>
       <c r="B260" t="inlineStr">
         <is>
           <t>Total</t>
@@ -3907,6 +5057,11 @@
       </c>
     </row>
     <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B262" t="inlineStr">
         <is>
           <t>Calera</t>
@@ -3920,6 +5075,11 @@
       </c>
     </row>
     <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B263" t="inlineStr">
         <is>
           <t>Chalchihuites</t>
@@ -3933,6 +5093,11 @@
       </c>
     </row>
     <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B264" t="inlineStr">
         <is>
           <t>Fresnillo</t>
@@ -3946,6 +5111,11 @@
       </c>
     </row>
     <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B265" t="inlineStr">
         <is>
           <t>Genaro Codina</t>
@@ -3959,6 +5129,11 @@
       </c>
     </row>
     <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B266" t="inlineStr">
         <is>
           <t>Jalpa</t>
@@ -3972,6 +5147,11 @@
       </c>
     </row>
     <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B267" t="inlineStr">
         <is>
           <t>Jerez</t>
@@ -3985,9 +5165,14 @@
       </c>
     </row>
     <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>Moyahua de Estrada</t>
+          <t>Moyahua De Estrada</t>
         </is>
       </c>
       <c r="C268">
@@ -3998,9 +5183,14 @@
       </c>
     </row>
     <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>Noria de Ángeles</t>
+          <t>Noria De Ángeles</t>
         </is>
       </c>
       <c r="C269">
@@ -4011,6 +5201,11 @@
       </c>
     </row>
     <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B270" t="inlineStr">
         <is>
           <t>Pinos</t>
@@ -4024,6 +5219,11 @@
       </c>
     </row>
     <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B271" t="inlineStr">
         <is>
           <t>Río Grande</t>
@@ -4037,6 +5237,11 @@
       </c>
     </row>
     <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B272" t="inlineStr">
         <is>
           <t>Sombrerete</t>
@@ -4050,9 +5255,14 @@
       </c>
     </row>
     <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>Teúl de González Ortega</t>
+          <t>Teúl De González Ortega</t>
         </is>
       </c>
       <c r="C273">
@@ -4063,9 +5273,14 @@
       </c>
     </row>
     <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>Tlaltenango de Sánchez Román</t>
+          <t>Tlaltenango De Sánchez Román</t>
         </is>
       </c>
       <c r="C274">
@@ -4076,6 +5291,11 @@
       </c>
     </row>
     <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B275" t="inlineStr">
         <is>
           <t>Valparaíso</t>
@@ -4089,9 +5309,14 @@
       </c>
     </row>
     <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>Villa de Cos</t>
+          <t>Villa De Cos</t>
         </is>
       </c>
       <c r="C276">
@@ -4102,6 +5327,11 @@
       </c>
     </row>
     <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B277" t="inlineStr">
         <is>
           <t>Villanueva</t>
@@ -4115,6 +5345,11 @@
       </c>
     </row>
     <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B278" t="inlineStr">
         <is>
           <t>Zacatecas</t>
@@ -4128,6 +5363,11 @@
       </c>
     </row>
     <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B279" t="inlineStr">
         <is>
           <t>Total</t>
@@ -4151,41 +5391,6 @@
       </c>
       <c r="D280">
         <v>1</v>
-      </c>
-    </row>
-    <row r="282">
-      <c r="A282" t="inlineStr">
-        <is>
-          <t>Tamaño de la muestra: 701,861</t>
-        </is>
-      </c>
-    </row>
-    <row r="283">
-      <c r="A283" t="inlineStr">
-        <is>
-          <t>Fuente: Expedición de Matrículas Consulares de Alta Seguridad en los Consulados de México en E.E.U.U.</t>
-        </is>
-      </c>
-    </row>
-    <row r="284">
-      <c r="A284" t="inlineStr">
-        <is>
-          <t>Elaborado por: Análisis de Información, Instituto de los Mexicanos en el Exterior</t>
-        </is>
-      </c>
-    </row>
-    <row r="285">
-      <c r="A285" t="inlineStr">
-        <is>
-          <t>Secretaría de Relaciones Exteriores</t>
-        </is>
-      </c>
-    </row>
-    <row r="286">
-      <c r="A286" t="inlineStr">
-        <is>
-          <t>Mayo de 2022</t>
-        </is>
       </c>
     </row>
   </sheetData>
